--- a/multi_regression/results_n_10_m_100_d_10/figs_100/regression_result.xlsx
+++ b/multi_regression/results_n_10_m_100_d_10/figs_100/regression_result.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0278 $\pm$ 0.0018</t>
+          <t>0.0274 $\pm$ 0.0020</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0278 $\pm$ 0.0018</t>
+          <t>0.0274 $\pm$ 0.0020</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0278 $\pm$ 0.0018</t>
+          <t>0.0274 $\pm$ 0.0020</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0278 $\pm$ 0.0018</t>
+          <t>0.0274 $\pm$ 0.0020</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.2513 $\pm$ 0.0512</t>
+          <t>0.2638 $\pm$ 0.0464</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.3803 $\pm$ 0.0951</t>
+          <t>0.5006 $\pm$ 0.2239</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.3550 $\pm$ 0.0848</t>
+          <t>0.4025 $\pm$ 0.0787</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.3090 $\pm$ 0.0692</t>
+          <t>0.3399 $\pm$ 0.0634</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.2054 $\pm$ 0.0169</t>
+          <t>0.2281 $\pm$ 0.0186</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.3654 $\pm$ 0.0729</t>
+          <t>0.3571 $\pm$ 0.0657</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.2641 $\pm$ 0.0187</t>
+          <t>0.4230 $\pm$ 0.0749</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.2325 $\pm$ 0.0180</t>
+          <t>0.3038 $\pm$ 0.0270</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5772.6929 $\pm$ 2749.9902</t>
+          <t>4262.1592 $\pm$ 2194.2590</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1148.6459 $\pm$ 2302.0329</t>
+          <t>78.8125 $\pm$ 232.8187</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3570.6595 $\pm$ 2345.3244</t>
+          <t>1702.1471 $\pm$ 1565.3104</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2333.9828 $\pm$ 1351.5244</t>
+          <t>4687.5654 $\pm$ 2952.4921</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.2730 $\pm$ 5.2348</t>
+          <t>25.4239 $\pm$ 2.8515</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>33.2629 $\pm$ 5.1985</t>
+          <t>37.6176 $\pm$ 3.7666</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.2225 $\pm$ 8.1370</t>
+          <t>46.1144 $\pm$ 4.8446</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3487 $\pm$ 7.0151</t>
+          <t>36.9225 $\pm$ 3.8934</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.8216 $\pm$ 0.6857</t>
+          <t>5301.3914 $\pm$ 1636.7111</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8.3765 $\pm$ 0.8658</t>
+          <t>1840.1012 $\pm$ 691.5574</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.9774 $\pm$ 1.0850</t>
+          <t>3232.8638 $\pm$ 650.6004</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.1644 $\pm$ 0.9067</t>
+          <t>3694.5003 $\pm$ 1537.1428</t>
         </is>
       </c>
     </row>
